--- a/MAPAS.xlsx
+++ b/MAPAS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GITHUB\coleccion-mapas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDA1DEFE-0B08-42A0-A152-2CD0FDB77950}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62D3CC14-B09D-41F3-A9D8-48CEB81B6FCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -587,7 +587,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -601,6 +601,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF0F4F8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
@@ -610,7 +615,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -644,643 +649,60 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFCCCCCC"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFCCCCCC"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFCCCCCC"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFCCCCCC"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FFCCCCCC"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFCCCCCC"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FFCCCCCC"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FFCCCCCC"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFCCCCCC"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFCCCCCC"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="18">
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Century Gothic"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FFCCCCCC"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color rgb="FFCCCCCC"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFCCCCCC"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Century Gothic"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FFCCCCCC"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFCCCCCC"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFCCCCCC"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFCCCCCC"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Century Gothic"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FFCCCCCC"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFCCCCCC"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFCCCCCC"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFCCCCCC"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Century Gothic"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="4" formatCode="#,##0.00"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FFCCCCCC"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFCCCCCC"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFCCCCCC"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFCCCCCC"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Century Gothic"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="4" formatCode="#,##0.00"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FFCCCCCC"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFCCCCCC"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFCCCCCC"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFCCCCCC"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Century Gothic"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="4" formatCode="#,##0.00"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FFCCCCCC"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFCCCCCC"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFCCCCCC"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFCCCCCC"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Century Gothic"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FFCCCCCC"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFCCCCCC"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFCCCCCC"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFCCCCCC"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Century Gothic"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FFCCCCCC"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFCCCCCC"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFCCCCCC"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFCCCCCC"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Century Gothic"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color rgb="FFCCCCCC"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFCCCCCC"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFCCCCCC"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <name val="Century Gothic"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF2E4057"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FFCCCCCC"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFCCCCCC"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color rgb="FFCCCCCC"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color rgb="FFCCCCCC"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFCCCCCC"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFCCCCCC"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFCCCCCC"/>
-        </bottom>
-      </border>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1291,29 +713,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{102C205E-32FF-48FB-A8CF-1B1567264E25}" name="Tabla1" displayName="Tabla1" ref="A1:N47" totalsRowShown="0" headerRowDxfId="15" dataDxfId="0" headerRowBorderDxfId="16" tableBorderDxfId="17">
-  <autoFilter ref="A1:N47" xr:uid="{102C205E-32FF-48FB-A8CF-1B1567264E25}"/>
-  <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{84883F2C-FBE0-49B0-B2A4-667ADC0551EE}" name="SKU" dataDxfId="14"/>
-    <tableColumn id="2" xr3:uid="{FA0C7CC0-8F44-4596-862E-23D742C3D87C}" name="Título" dataDxfId="13"/>
-    <tableColumn id="3" xr3:uid="{940B6288-0BBE-4C24-9F5A-F00B728349AE}" name="Autor/es" dataDxfId="12"/>
-    <tableColumn id="4" xr3:uid="{EB339503-DADC-4498-BDD0-E2BB3AF48019}" name="Fecha del mapa" dataDxfId="11"/>
-    <tableColumn id="5" xr3:uid="{3EFDA8C6-E78A-46A7-8942-28F581BC398C}" name="Dimensiones (cm)" dataDxfId="10"/>
-    <tableColumn id="6" xr3:uid="{04A8DE57-680E-4FA0-8802-A35B0E5DE92A}" name="Coloreado" dataDxfId="9"/>
-    <tableColumn id="7" xr3:uid="{F55CF3BD-3875-42E3-A772-0795514B31AE}" name="Fecha de compra" dataDxfId="8"/>
-    <tableColumn id="8" xr3:uid="{6E6EF76B-92B3-481A-8843-C0118754E312}" name="Vendedor" dataDxfId="7"/>
-    <tableColumn id="9" xr3:uid="{E523DE7F-11BD-41ED-91E0-1B21FCAA9E18}" name="Precio" dataDxfId="6"/>
-    <tableColumn id="10" xr3:uid="{FAB62673-0B84-4D34-ACC2-FEF063E2634A}" name="Portes" dataDxfId="5"/>
-    <tableColumn id="11" xr3:uid="{CEC4007D-7037-4039-895A-EDFFF684FE1B}" name="Total" dataDxfId="4"/>
-    <tableColumn id="12" xr3:uid="{127D4E27-9485-492D-BEF8-C64A801B4DDB}" name="Archivador" dataDxfId="3"/>
-    <tableColumn id="13" xr3:uid="{E8425AA7-5A64-4D68-8059-563620A2EAA8}" name="Notas" dataDxfId="2"/>
-    <tableColumn id="14" xr3:uid="{55C09031-CF0F-43DE-BCAC-DE7085D7E307}" name="Anotaciones" dataDxfId="1"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight18" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1601,2085 +1000,1810 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T49"/>
+  <dimension ref="A1:N49"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
     <col min="2" max="3" width="45" customWidth="1"/>
-    <col min="4" max="4" width="19.21875" customWidth="1"/>
-    <col min="5" max="5" width="20.6640625" customWidth="1"/>
-    <col min="6" max="6" width="13.5546875" customWidth="1"/>
-    <col min="7" max="7" width="20.77734375" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="7" max="7" width="15" customWidth="1"/>
     <col min="8" max="8" width="22" customWidth="1"/>
     <col min="9" max="11" width="11" customWidth="1"/>
-    <col min="12" max="12" width="13.77734375" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
     <col min="13" max="14" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="8" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="10">
+    <row r="2" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="2">
         <v>139</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="11">
+      <c r="D2" s="2">
         <v>1798</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="F2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="G2" s="11" t="s">
+      <c r="G2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="H2" s="12" t="s">
+      <c r="H2" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="I2" s="13">
+      <c r="I2" s="4">
         <v>28</v>
       </c>
-      <c r="J2" s="13">
+      <c r="J2" s="4">
         <v>8</v>
       </c>
-      <c r="K2" s="13">
+      <c r="K2" s="4">
         <v>36</v>
       </c>
-      <c r="L2" s="11" t="s">
+      <c r="L2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="M2" s="9" t="s">
+      <c r="M2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="14"/>
-      <c r="O2" s="15"/>
-      <c r="P2" s="15"/>
-      <c r="Q2" s="15"/>
-      <c r="R2" s="15"/>
-      <c r="S2" s="15"/>
-      <c r="T2" s="15"/>
-    </row>
-    <row r="3" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="10">
+      <c r="N2" s="3"/>
+    </row>
+    <row r="3" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="5">
         <v>140</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="11">
+      <c r="D3" s="5">
         <v>1798</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="F3" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="11" t="s">
+      <c r="G3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="H3" s="12" t="s">
+      <c r="H3" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="I3" s="13">
+      <c r="I3" s="7">
         <v>28</v>
       </c>
-      <c r="J3" s="13">
+      <c r="J3" s="7">
         <v>8</v>
       </c>
-      <c r="K3" s="13">
+      <c r="K3" s="7">
         <v>36</v>
       </c>
-      <c r="L3" s="11" t="s">
+      <c r="L3" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="M3" s="9" t="s">
+      <c r="M3" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="N3" s="14"/>
-      <c r="O3" s="15"/>
-      <c r="P3" s="15"/>
-      <c r="Q3" s="15"/>
-      <c r="R3" s="15"/>
-      <c r="S3" s="15"/>
-      <c r="T3" s="15"/>
-    </row>
-    <row r="4" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="10">
+      <c r="N3" s="6"/>
+    </row>
+    <row r="4" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
         <v>175</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="F4" s="16" t="s">
+      <c r="F4" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="H4" s="12" t="s">
+      <c r="H4" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="I4" s="13">
+      <c r="I4" s="4">
         <v>69</v>
       </c>
-      <c r="J4" s="13">
+      <c r="J4" s="4">
         <v>16</v>
       </c>
-      <c r="K4" s="13">
+      <c r="K4" s="4">
         <v>85</v>
       </c>
-      <c r="L4" s="11"/>
-      <c r="M4" s="12" t="s">
+      <c r="L4" s="2"/>
+      <c r="M4" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="N4" s="17" t="s">
+      <c r="N4" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="O4" s="15"/>
-      <c r="P4" s="15"/>
-      <c r="Q4" s="15"/>
-      <c r="R4" s="15"/>
-      <c r="S4" s="15"/>
-      <c r="T4" s="15"/>
-    </row>
-    <row r="5" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="10">
+    </row>
+    <row r="5" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="5">
         <v>219</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="D5" s="11">
+      <c r="D5" s="5">
         <v>1780</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="E5" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="F5" s="16" t="s">
+      <c r="F5" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="G5" s="11" t="s">
+      <c r="G5" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="H5" s="9" t="s">
+      <c r="H5" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="I5" s="13">
+      <c r="I5" s="7">
         <v>30</v>
       </c>
-      <c r="J5" s="13">
+      <c r="J5" s="7">
         <v>15</v>
       </c>
-      <c r="K5" s="13">
+      <c r="K5" s="7">
         <v>45</v>
       </c>
-      <c r="L5" s="11" t="s">
+      <c r="L5" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="M5" s="12" t="s">
+      <c r="M5" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="N5" s="14"/>
-      <c r="O5" s="15"/>
-      <c r="P5" s="15"/>
-      <c r="Q5" s="15"/>
-      <c r="R5" s="15"/>
-      <c r="S5" s="15"/>
-      <c r="T5" s="15"/>
-    </row>
-    <row r="6" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="10">
+      <c r="N5" s="6"/>
+    </row>
+    <row r="6" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
         <v>230</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="D6" s="11">
+      <c r="D6" s="2">
         <v>1635</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="F6" s="16" t="s">
+      <c r="F6" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G6" s="11" t="s">
+      <c r="G6" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="H6" s="9" t="s">
+      <c r="H6" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="I6" s="13">
+      <c r="I6" s="4">
         <v>45</v>
       </c>
-      <c r="J6" s="13">
+      <c r="J6" s="4">
         <v>15</v>
       </c>
-      <c r="K6" s="13">
+      <c r="K6" s="4">
         <v>60</v>
       </c>
-      <c r="L6" s="11"/>
-      <c r="M6" s="12" t="s">
+      <c r="L6" s="2"/>
+      <c r="M6" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="N6" s="14"/>
-      <c r="O6" s="15"/>
-      <c r="P6" s="15"/>
-      <c r="Q6" s="15"/>
-      <c r="R6" s="15"/>
-      <c r="S6" s="15"/>
-      <c r="T6" s="15"/>
-    </row>
-    <row r="7" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="10">
+      <c r="N6" s="3"/>
+    </row>
+    <row r="7" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="5">
         <v>574</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="D7" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="E7" s="9"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="11" t="s">
+      <c r="E7" s="6"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="H7" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="I7" s="13">
+      <c r="H7" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="I7" s="7">
         <v>74</v>
       </c>
-      <c r="J7" s="13">
+      <c r="J7" s="7">
         <v>22</v>
       </c>
-      <c r="K7" s="13">
+      <c r="K7" s="7">
         <v>96</v>
       </c>
-      <c r="L7" s="11" t="s">
+      <c r="L7" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="M7" s="9"/>
-      <c r="N7" s="14"/>
-      <c r="O7" s="15"/>
-      <c r="P7" s="15"/>
-      <c r="Q7" s="15"/>
-      <c r="R7" s="15"/>
-      <c r="S7" s="15"/>
-      <c r="T7" s="15"/>
-    </row>
-    <row r="8" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="10">
+      <c r="M7" s="6"/>
+      <c r="N7" s="6"/>
+    </row>
+    <row r="8" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
         <v>575</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="D8" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="E8" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="F8" s="16" t="s">
+      <c r="F8" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G8" s="11" t="s">
+      <c r="G8" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="H8" s="12" t="s">
+      <c r="H8" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="I8" s="13">
+      <c r="I8" s="4">
         <v>34</v>
       </c>
-      <c r="J8" s="13">
+      <c r="J8" s="4">
         <v>4</v>
       </c>
-      <c r="K8" s="13">
+      <c r="K8" s="4">
         <v>38</v>
       </c>
-      <c r="L8" s="11"/>
-      <c r="M8" s="9" t="s">
+      <c r="L8" s="2"/>
+      <c r="M8" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="N8" s="14"/>
-      <c r="O8" s="15"/>
-      <c r="P8" s="15"/>
-      <c r="Q8" s="15"/>
-      <c r="R8" s="15"/>
-      <c r="S8" s="15"/>
-      <c r="T8" s="15"/>
-    </row>
-    <row r="9" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="10">
+      <c r="N8" s="3"/>
+    </row>
+    <row r="9" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="5">
         <v>576</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="D9" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="E9" s="12" t="s">
+      <c r="E9" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="F9" s="16" t="s">
+      <c r="F9" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="G9" s="11" t="s">
+      <c r="G9" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="H9" s="12" t="s">
+      <c r="H9" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="I9" s="13">
+      <c r="I9" s="7">
         <v>34</v>
       </c>
-      <c r="J9" s="13">
+      <c r="J9" s="7">
         <v>4</v>
       </c>
-      <c r="K9" s="13">
+      <c r="K9" s="7">
         <v>38</v>
       </c>
-      <c r="L9" s="11"/>
-      <c r="M9" s="9" t="s">
+      <c r="L9" s="5"/>
+      <c r="M9" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="N9" s="14"/>
-      <c r="O9" s="15"/>
-      <c r="P9" s="15"/>
-      <c r="Q9" s="15"/>
-      <c r="R9" s="15"/>
-      <c r="S9" s="15"/>
-      <c r="T9" s="15"/>
-    </row>
-    <row r="10" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="10">
+      <c r="N9" s="6"/>
+    </row>
+    <row r="10" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="2">
         <v>577</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C10" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="11" t="s">
+      <c r="D10" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="E10" s="9"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11" t="s">
+      <c r="E10" s="3"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="H10" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="I10" s="13">
+      <c r="H10" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="I10" s="4">
         <v>56</v>
       </c>
-      <c r="J10" s="13">
+      <c r="J10" s="4">
         <v>8</v>
       </c>
-      <c r="K10" s="13">
+      <c r="K10" s="4">
         <v>64</v>
       </c>
-      <c r="L10" s="11" t="s">
+      <c r="L10" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="M10" s="9"/>
-      <c r="N10" s="14"/>
-      <c r="O10" s="15"/>
-      <c r="P10" s="15"/>
-      <c r="Q10" s="15"/>
-      <c r="R10" s="15"/>
-      <c r="S10" s="15"/>
-      <c r="T10" s="15"/>
-    </row>
-    <row r="11" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="10">
+      <c r="M10" s="3"/>
+      <c r="N10" s="3"/>
+    </row>
+    <row r="11" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="5">
         <v>578</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="D11" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="E11" s="9"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11" t="s">
+      <c r="E11" s="6"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="H11" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="I11" s="13">
+      <c r="H11" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="I11" s="7">
         <v>56</v>
       </c>
-      <c r="J11" s="13">
+      <c r="J11" s="7">
         <v>8</v>
       </c>
-      <c r="K11" s="13">
+      <c r="K11" s="7">
         <v>64</v>
       </c>
-      <c r="L11" s="11" t="s">
+      <c r="L11" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="M11" s="9"/>
-      <c r="N11" s="14"/>
-      <c r="O11" s="15"/>
-      <c r="P11" s="15"/>
-      <c r="Q11" s="15"/>
-      <c r="R11" s="15"/>
-      <c r="S11" s="15"/>
-      <c r="T11" s="15"/>
-    </row>
-    <row r="12" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="10">
+      <c r="M11" s="6"/>
+      <c r="N11" s="6"/>
+    </row>
+    <row r="12" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="2">
         <v>579</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="C12" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D12" s="11"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11" t="s">
+      <c r="D12" s="2"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="H12" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="I12" s="13">
+      <c r="H12" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="I12" s="4">
         <v>142</v>
       </c>
-      <c r="J12" s="13">
+      <c r="J12" s="4">
         <v>11</v>
       </c>
-      <c r="K12" s="13">
+      <c r="K12" s="4">
         <v>153</v>
       </c>
-      <c r="L12" s="11" t="s">
+      <c r="L12" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="M12" s="9"/>
-      <c r="N12" s="14"/>
-      <c r="O12" s="15"/>
-      <c r="P12" s="15"/>
-      <c r="Q12" s="15"/>
-      <c r="R12" s="15"/>
-      <c r="S12" s="15"/>
-      <c r="T12" s="15"/>
-    </row>
-    <row r="13" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="10">
+      <c r="M12" s="3"/>
+      <c r="N12" s="3"/>
+    </row>
+    <row r="13" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="5">
         <v>580</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C13" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="D13" s="11">
+      <c r="D13" s="5">
         <v>1754</v>
       </c>
-      <c r="E13" s="9" t="s">
+      <c r="E13" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="F13" s="11" t="s">
+      <c r="F13" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="G13" s="11" t="s">
+      <c r="G13" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="H13" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="I13" s="13">
+      <c r="H13" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="I13" s="7">
         <v>40</v>
       </c>
-      <c r="J13" s="13">
+      <c r="J13" s="7">
         <v>11</v>
       </c>
-      <c r="K13" s="13">
+      <c r="K13" s="7">
         <v>51</v>
       </c>
-      <c r="L13" s="11" t="s">
+      <c r="L13" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="M13" s="9"/>
-      <c r="N13" s="14"/>
-      <c r="O13" s="15"/>
-      <c r="P13" s="15"/>
-      <c r="Q13" s="15"/>
-      <c r="R13" s="15"/>
-      <c r="S13" s="15"/>
-      <c r="T13" s="15"/>
-    </row>
-    <row r="14" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="10">
+      <c r="M13" s="6"/>
+      <c r="N13" s="6"/>
+    </row>
+    <row r="14" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="2">
         <v>581</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C14" s="9"/>
-      <c r="D14" s="11" t="s">
+      <c r="C14" s="3"/>
+      <c r="D14" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="E14" s="9"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="11" t="s">
+      <c r="E14" s="3"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="H14" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="I14" s="13">
+      <c r="H14" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="I14" s="4">
         <v>90</v>
       </c>
-      <c r="J14" s="13">
+      <c r="J14" s="4">
         <v>20</v>
       </c>
-      <c r="K14" s="13">
+      <c r="K14" s="4">
         <v>110</v>
       </c>
-      <c r="L14" s="11" t="s">
+      <c r="L14" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="M14" s="9"/>
-      <c r="N14" s="14"/>
-      <c r="O14" s="15"/>
-      <c r="P14" s="15"/>
-      <c r="Q14" s="15"/>
-      <c r="R14" s="15"/>
-      <c r="S14" s="15"/>
-      <c r="T14" s="15"/>
-    </row>
-    <row r="15" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="10">
+      <c r="M14" s="3"/>
+      <c r="N14" s="3"/>
+    </row>
+    <row r="15" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="5">
         <v>582</v>
       </c>
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="C15" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="D15" s="11" t="s">
+      <c r="D15" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="E15" s="9"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="11" t="s">
+      <c r="E15" s="6"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="H15" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="I15" s="13">
+      <c r="H15" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="I15" s="7">
         <v>112</v>
       </c>
-      <c r="J15" s="13">
+      <c r="J15" s="7">
         <v>20</v>
       </c>
-      <c r="K15" s="13">
+      <c r="K15" s="7">
         <v>132</v>
       </c>
-      <c r="L15" s="11" t="s">
+      <c r="L15" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="M15" s="9"/>
-      <c r="N15" s="14"/>
-      <c r="O15" s="15"/>
-      <c r="P15" s="15"/>
-      <c r="Q15" s="15"/>
-      <c r="R15" s="15"/>
-      <c r="S15" s="15"/>
-      <c r="T15" s="15"/>
-    </row>
-    <row r="16" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="10">
+      <c r="M15" s="6"/>
+      <c r="N15" s="6"/>
+    </row>
+    <row r="16" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="2">
         <v>583</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C16" s="9" t="s">
+      <c r="C16" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="D16" s="11">
+      <c r="D16" s="2">
         <v>1754</v>
       </c>
-      <c r="E16" s="9" t="s">
+      <c r="E16" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="F16" s="11" t="s">
+      <c r="F16" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="G16" s="11" t="s">
+      <c r="G16" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="H16" s="12" t="s">
+      <c r="H16" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="I16" s="13">
+      <c r="I16" s="4">
         <v>24</v>
       </c>
-      <c r="J16" s="13"/>
-      <c r="K16" s="13">
+      <c r="J16" s="4"/>
+      <c r="K16" s="4">
         <v>24</v>
       </c>
-      <c r="L16" s="11" t="s">
+      <c r="L16" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="M16" s="9" t="s">
+      <c r="M16" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="N16" s="14"/>
-      <c r="O16" s="15"/>
-      <c r="P16" s="15"/>
-      <c r="Q16" s="15"/>
-      <c r="R16" s="15"/>
-      <c r="S16" s="15"/>
-      <c r="T16" s="15"/>
-    </row>
-    <row r="17" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="10">
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="5">
         <v>584</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="B17" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="C17" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="D17" s="11">
+      <c r="D17" s="5">
         <v>1754</v>
       </c>
-      <c r="E17" s="9" t="s">
+      <c r="E17" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="F17" s="11" t="s">
+      <c r="F17" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G17" s="11" t="s">
+      <c r="G17" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="H17" s="12" t="s">
+      <c r="H17" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="I17" s="13">
+      <c r="I17" s="7">
         <v>24</v>
       </c>
-      <c r="J17" s="13"/>
-      <c r="K17" s="13">
+      <c r="J17" s="7"/>
+      <c r="K17" s="7">
         <v>24</v>
       </c>
-      <c r="L17" s="11" t="s">
+      <c r="L17" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="M17" s="9" t="s">
+      <c r="M17" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="N17" s="14"/>
-      <c r="O17" s="15"/>
-      <c r="P17" s="15"/>
-      <c r="Q17" s="15"/>
-      <c r="R17" s="15"/>
-      <c r="S17" s="15"/>
-      <c r="T17" s="15"/>
-    </row>
-    <row r="18" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="10">
+      <c r="N17" s="6"/>
+    </row>
+    <row r="18" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="2">
         <v>585</v>
       </c>
-      <c r="B18" s="9" t="s">
+      <c r="B18" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="C18" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="D18" s="11">
+      <c r="D18" s="2">
         <v>1774</v>
       </c>
-      <c r="E18" s="9" t="s">
+      <c r="E18" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="F18" s="11" t="s">
+      <c r="F18" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="G18" s="11" t="s">
+      <c r="G18" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="H18" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="I18" s="13">
+      <c r="H18" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="I18" s="4">
         <v>30</v>
       </c>
-      <c r="J18" s="13">
+      <c r="J18" s="4">
         <v>7.5</v>
       </c>
-      <c r="K18" s="13">
+      <c r="K18" s="4">
         <v>37.5</v>
       </c>
-      <c r="L18" s="11" t="s">
+      <c r="L18" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="M18" s="9" t="s">
+      <c r="M18" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="N18" s="14"/>
-      <c r="O18" s="15"/>
-      <c r="P18" s="15"/>
-      <c r="Q18" s="15"/>
-      <c r="R18" s="15"/>
-      <c r="S18" s="15"/>
-      <c r="T18" s="15"/>
-    </row>
-    <row r="19" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="10">
+      <c r="N18" s="3"/>
+    </row>
+    <row r="19" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="5">
         <v>586</v>
       </c>
-      <c r="B19" s="9" t="s">
+      <c r="B19" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="C19" s="9" t="s">
+      <c r="C19" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="D19" s="11"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="11" t="s">
+      <c r="D19" s="5"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="H19" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="I19" s="13">
+      <c r="H19" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="I19" s="7">
         <v>91</v>
       </c>
-      <c r="J19" s="13">
+      <c r="J19" s="7">
         <v>16</v>
       </c>
-      <c r="K19" s="13">
+      <c r="K19" s="7">
         <v>107</v>
       </c>
-      <c r="L19" s="11" t="s">
+      <c r="L19" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="M19" s="9"/>
-      <c r="N19" s="14"/>
-      <c r="O19" s="15"/>
-      <c r="P19" s="15"/>
-      <c r="Q19" s="15"/>
-      <c r="R19" s="15"/>
-      <c r="S19" s="15"/>
-      <c r="T19" s="15"/>
-    </row>
-    <row r="20" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="10">
+      <c r="M19" s="6"/>
+      <c r="N19" s="6"/>
+    </row>
+    <row r="20" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="2">
         <v>587</v>
       </c>
-      <c r="B20" s="9" t="s">
+      <c r="B20" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C20" s="9" t="s">
+      <c r="C20" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="D20" s="11"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="11"/>
-      <c r="G20" s="11" t="s">
+      <c r="D20" s="2"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="H20" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="I20" s="13">
+      <c r="H20" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="I20" s="4">
         <v>91</v>
       </c>
-      <c r="J20" s="13">
+      <c r="J20" s="4">
         <v>22</v>
       </c>
-      <c r="K20" s="13">
+      <c r="K20" s="4">
         <v>113</v>
       </c>
-      <c r="L20" s="11" t="s">
+      <c r="L20" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="M20" s="9"/>
-      <c r="N20" s="14"/>
-      <c r="O20" s="15"/>
-      <c r="P20" s="15"/>
-      <c r="Q20" s="15"/>
-      <c r="R20" s="15"/>
-      <c r="S20" s="15"/>
-      <c r="T20" s="15"/>
-    </row>
-    <row r="21" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="10">
+      <c r="M20" s="3"/>
+      <c r="N20" s="3"/>
+    </row>
+    <row r="21" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="2">
         <v>588</v>
       </c>
-      <c r="B21" s="9" t="s">
+      <c r="B21" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="C21" s="9" t="s">
+      <c r="C21" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="D21" s="11">
+      <c r="D21" s="2">
         <v>1787</v>
       </c>
-      <c r="E21" s="9" t="s">
+      <c r="E21" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="F21" s="11" t="s">
+      <c r="F21" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="G21" s="11" t="s">
+      <c r="G21" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="H21" s="9" t="s">
+      <c r="H21" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="I21" s="13">
+      <c r="I21" s="4">
         <v>112</v>
       </c>
-      <c r="J21" s="13">
+      <c r="J21" s="4">
         <v>11</v>
       </c>
-      <c r="K21" s="13">
+      <c r="K21" s="4">
         <v>123</v>
       </c>
-      <c r="L21" s="11" t="s">
+      <c r="L21" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="M21" s="9" t="s">
+      <c r="M21" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="N21" s="14"/>
-      <c r="O21" s="15"/>
-      <c r="P21" s="15"/>
-      <c r="Q21" s="15"/>
-      <c r="R21" s="15"/>
-      <c r="S21" s="15"/>
-      <c r="T21" s="15"/>
-    </row>
-    <row r="22" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="10">
+      <c r="N21" s="3"/>
+    </row>
+    <row r="22" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="5">
         <v>589</v>
       </c>
-      <c r="B22" s="9" t="s">
+      <c r="B22" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="C22" s="9" t="s">
+      <c r="C22" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="D22" s="11">
+      <c r="D22" s="5">
         <v>1780</v>
       </c>
-      <c r="E22" s="9" t="s">
+      <c r="E22" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="F22" s="11" t="s">
+      <c r="F22" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G22" s="11" t="s">
+      <c r="G22" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="H22" s="9" t="s">
+      <c r="H22" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="I22" s="13">
+      <c r="I22" s="7">
         <v>51</v>
       </c>
-      <c r="J22" s="13">
+      <c r="J22" s="7">
         <v>11</v>
       </c>
-      <c r="K22" s="13">
+      <c r="K22" s="7">
         <v>62</v>
       </c>
-      <c r="L22" s="11" t="s">
+      <c r="L22" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="M22" s="9" t="s">
+      <c r="M22" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="N22" s="14"/>
-      <c r="O22" s="15"/>
-      <c r="P22" s="15"/>
-      <c r="Q22" s="15"/>
-      <c r="R22" s="15"/>
-      <c r="S22" s="15"/>
-      <c r="T22" s="15"/>
-    </row>
-    <row r="23" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="10">
+      <c r="N22" s="6"/>
+    </row>
+    <row r="23" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="2">
         <v>590</v>
       </c>
-      <c r="B23" s="9" t="s">
+      <c r="B23" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C23" s="9" t="s">
+      <c r="C23" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="D23" s="11"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="11"/>
-      <c r="G23" s="11" t="s">
+      <c r="D23" s="2"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="H23" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="I23" s="13">
+      <c r="H23" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="I23" s="4">
         <v>28</v>
       </c>
-      <c r="J23" s="13"/>
-      <c r="K23" s="13">
+      <c r="J23" s="4"/>
+      <c r="K23" s="4">
         <v>28</v>
       </c>
-      <c r="L23" s="11" t="s">
+      <c r="L23" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="M23" s="9"/>
-      <c r="N23" s="14"/>
-      <c r="O23" s="15"/>
-      <c r="P23" s="15"/>
-      <c r="Q23" s="15"/>
-      <c r="R23" s="15"/>
-      <c r="S23" s="15"/>
-      <c r="T23" s="15"/>
-    </row>
-    <row r="24" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="10">
+      <c r="M23" s="3"/>
+      <c r="N23" s="3"/>
+    </row>
+    <row r="24" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="5">
         <v>591</v>
       </c>
-      <c r="B24" s="9" t="s">
+      <c r="B24" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="C24" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="D24" s="11"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="11"/>
-      <c r="G24" s="11" t="s">
+      <c r="D24" s="5"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="H24" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="I24" s="13">
+      <c r="H24" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="I24" s="7">
         <v>28</v>
       </c>
-      <c r="J24" s="13"/>
-      <c r="K24" s="13">
+      <c r="J24" s="7"/>
+      <c r="K24" s="7">
         <v>28</v>
       </c>
-      <c r="L24" s="11" t="s">
+      <c r="L24" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="M24" s="9"/>
-      <c r="N24" s="14"/>
-      <c r="O24" s="15"/>
-      <c r="P24" s="15"/>
-      <c r="Q24" s="15"/>
-      <c r="R24" s="15"/>
-      <c r="S24" s="15"/>
-      <c r="T24" s="15"/>
-    </row>
-    <row r="25" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="10">
+      <c r="M24" s="6"/>
+      <c r="N24" s="6"/>
+    </row>
+    <row r="25" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="5">
         <v>592</v>
       </c>
-      <c r="B25" s="9" t="s">
+      <c r="B25" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="C25" s="9" t="s">
+      <c r="C25" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D25" s="11"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="11"/>
-      <c r="G25" s="11"/>
-      <c r="H25" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="I25" s="13">
+      <c r="D25" s="5"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="I25" s="7">
         <v>112</v>
       </c>
-      <c r="J25" s="13">
+      <c r="J25" s="7">
         <v>22</v>
       </c>
-      <c r="K25" s="13">
+      <c r="K25" s="7">
         <v>134</v>
       </c>
-      <c r="L25" s="11" t="s">
+      <c r="L25" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="M25" s="9"/>
-      <c r="N25" s="14"/>
-      <c r="O25" s="15"/>
-      <c r="P25" s="15"/>
-      <c r="Q25" s="15"/>
-      <c r="R25" s="15"/>
-      <c r="S25" s="15"/>
-      <c r="T25" s="15"/>
-    </row>
-    <row r="26" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="10">
+      <c r="M25" s="6"/>
+      <c r="N25" s="6"/>
+    </row>
+    <row r="26" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="2">
         <v>593</v>
       </c>
-      <c r="B26" s="9" t="s">
+      <c r="B26" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C26" s="9" t="s">
+      <c r="C26" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="D26" s="11"/>
-      <c r="E26" s="9"/>
-      <c r="F26" s="11"/>
-      <c r="G26" s="11" t="s">
+      <c r="D26" s="2"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="H26" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="I26" s="13">
+      <c r="H26" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="I26" s="4">
         <v>106</v>
       </c>
-      <c r="J26" s="13">
+      <c r="J26" s="4">
         <v>11</v>
       </c>
-      <c r="K26" s="13">
+      <c r="K26" s="4">
         <v>117</v>
       </c>
-      <c r="L26" s="11" t="s">
+      <c r="L26" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="M26" s="9"/>
-      <c r="N26" s="14"/>
-      <c r="O26" s="15"/>
-      <c r="P26" s="15"/>
-      <c r="Q26" s="15"/>
-      <c r="R26" s="15"/>
-      <c r="S26" s="15"/>
-      <c r="T26" s="15"/>
-    </row>
-    <row r="27" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="10">
+      <c r="M26" s="3"/>
+      <c r="N26" s="3"/>
+    </row>
+    <row r="27" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="5">
         <v>594</v>
       </c>
-      <c r="B27" s="9" t="s">
+      <c r="B27" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="C27" s="9" t="s">
+      <c r="C27" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="D27" s="11"/>
-      <c r="E27" s="9"/>
-      <c r="F27" s="11"/>
-      <c r="G27" s="11" t="s">
+      <c r="D27" s="5"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="H27" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="I27" s="13">
+      <c r="H27" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="I27" s="7">
         <v>83</v>
       </c>
-      <c r="J27" s="13">
+      <c r="J27" s="7">
         <v>11</v>
       </c>
-      <c r="K27" s="13">
+      <c r="K27" s="7">
         <v>94</v>
       </c>
-      <c r="L27" s="11" t="s">
+      <c r="L27" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="M27" s="9"/>
-      <c r="N27" s="14"/>
-      <c r="O27" s="15"/>
-      <c r="P27" s="15"/>
-      <c r="Q27" s="15"/>
-      <c r="R27" s="15"/>
-      <c r="S27" s="15"/>
-      <c r="T27" s="15"/>
-    </row>
-    <row r="28" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="10">
+      <c r="M27" s="6"/>
+      <c r="N27" s="6"/>
+    </row>
+    <row r="28" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="2">
         <v>595</v>
       </c>
-      <c r="B28" s="9" t="s">
+      <c r="B28" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="C28" s="9" t="s">
+      <c r="C28" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="D28" s="11"/>
-      <c r="E28" s="9"/>
-      <c r="F28" s="11"/>
-      <c r="G28" s="11" t="s">
+      <c r="D28" s="2"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="H28" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="I28" s="13">
+      <c r="H28" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="I28" s="4">
         <v>13</v>
       </c>
-      <c r="J28" s="13">
+      <c r="J28" s="4">
         <v>6</v>
       </c>
-      <c r="K28" s="13">
+      <c r="K28" s="4">
         <v>19</v>
       </c>
-      <c r="L28" s="11" t="s">
+      <c r="L28" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="M28" s="9"/>
-      <c r="N28" s="14"/>
-      <c r="O28" s="15"/>
-      <c r="P28" s="15"/>
-      <c r="Q28" s="15"/>
-      <c r="R28" s="15"/>
-      <c r="S28" s="15"/>
-      <c r="T28" s="15"/>
-    </row>
-    <row r="29" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="10">
+      <c r="M28" s="3"/>
+      <c r="N28" s="3"/>
+    </row>
+    <row r="29" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="5">
         <v>596</v>
       </c>
-      <c r="B29" s="9" t="s">
+      <c r="B29" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="C29" s="9" t="s">
+      <c r="C29" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="D29" s="11"/>
-      <c r="E29" s="9"/>
-      <c r="F29" s="11"/>
-      <c r="G29" s="11" t="s">
+      <c r="D29" s="5"/>
+      <c r="E29" s="6"/>
+      <c r="F29" s="5"/>
+      <c r="G29" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="H29" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="I29" s="13">
+      <c r="H29" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="I29" s="7">
         <v>13</v>
       </c>
-      <c r="J29" s="13">
+      <c r="J29" s="7">
         <v>6</v>
       </c>
-      <c r="K29" s="13">
+      <c r="K29" s="7">
         <v>19</v>
       </c>
-      <c r="L29" s="11" t="s">
+      <c r="L29" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="M29" s="9"/>
-      <c r="N29" s="14"/>
-      <c r="O29" s="15"/>
-      <c r="P29" s="15"/>
-      <c r="Q29" s="15"/>
-      <c r="R29" s="15"/>
-      <c r="S29" s="15"/>
-      <c r="T29" s="15"/>
-    </row>
-    <row r="30" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="10">
+      <c r="M29" s="6"/>
+      <c r="N29" s="6"/>
+    </row>
+    <row r="30" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="2">
         <v>597</v>
       </c>
-      <c r="B30" s="9" t="s">
+      <c r="B30" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="C30" s="9" t="s">
+      <c r="C30" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="D30" s="11"/>
-      <c r="E30" s="9"/>
-      <c r="F30" s="11"/>
-      <c r="G30" s="11" t="s">
+      <c r="D30" s="2"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="H30" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="I30" s="13">
+      <c r="H30" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="I30" s="4">
         <v>56</v>
       </c>
-      <c r="J30" s="13">
+      <c r="J30" s="4">
         <v>11</v>
       </c>
-      <c r="K30" s="13">
+      <c r="K30" s="4">
         <v>67</v>
       </c>
-      <c r="L30" s="11" t="s">
+      <c r="L30" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="M30" s="9"/>
-      <c r="N30" s="14"/>
-      <c r="O30" s="15"/>
-      <c r="P30" s="15"/>
-      <c r="Q30" s="15"/>
-      <c r="R30" s="15"/>
-      <c r="S30" s="15"/>
-      <c r="T30" s="15"/>
-    </row>
-    <row r="31" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="10">
+      <c r="M30" s="3"/>
+      <c r="N30" s="3"/>
+    </row>
+    <row r="31" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="5">
         <v>598</v>
       </c>
-      <c r="B31" s="9" t="s">
+      <c r="B31" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="C31" s="9" t="s">
+      <c r="C31" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="D31" s="11" t="s">
+      <c r="D31" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="E31" s="9"/>
-      <c r="F31" s="11"/>
-      <c r="G31" s="11" t="s">
+      <c r="E31" s="6"/>
+      <c r="F31" s="5"/>
+      <c r="G31" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="H31" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="I31" s="13">
+      <c r="H31" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="I31" s="7">
         <v>30</v>
       </c>
-      <c r="J31" s="13">
+      <c r="J31" s="7">
         <v>28</v>
       </c>
-      <c r="K31" s="13">
+      <c r="K31" s="7">
         <v>58</v>
       </c>
-      <c r="L31" s="11" t="s">
+      <c r="L31" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="M31" s="9"/>
-      <c r="N31" s="14"/>
-      <c r="O31" s="15"/>
-      <c r="P31" s="15"/>
-      <c r="Q31" s="15"/>
-      <c r="R31" s="15"/>
-      <c r="S31" s="15"/>
-      <c r="T31" s="15"/>
-    </row>
-    <row r="32" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="10">
+      <c r="M31" s="6"/>
+      <c r="N31" s="6"/>
+    </row>
+    <row r="32" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="2">
         <v>599</v>
       </c>
-      <c r="B32" s="9" t="s">
+      <c r="B32" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="C32" s="9" t="s">
+      <c r="C32" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D32" s="11" t="s">
+      <c r="D32" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E32" s="9"/>
-      <c r="F32" s="11"/>
-      <c r="G32" s="11" t="s">
+      <c r="E32" s="3"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="H32" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="I32" s="13">
+      <c r="H32" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="I32" s="4">
         <v>73</v>
       </c>
-      <c r="J32" s="13">
+      <c r="J32" s="4">
         <v>19</v>
       </c>
-      <c r="K32" s="13">
+      <c r="K32" s="4">
         <v>92</v>
       </c>
-      <c r="L32" s="11"/>
-      <c r="M32" s="9"/>
-      <c r="N32" s="14"/>
-      <c r="O32" s="15"/>
-      <c r="P32" s="15"/>
-      <c r="Q32" s="15"/>
-      <c r="R32" s="15"/>
-      <c r="S32" s="15"/>
-      <c r="T32" s="15"/>
-    </row>
-    <row r="33" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="10">
+      <c r="L32" s="2"/>
+      <c r="M32" s="3"/>
+      <c r="N32" s="3"/>
+    </row>
+    <row r="33" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="5">
         <v>600</v>
       </c>
-      <c r="B33" s="9" t="s">
+      <c r="B33" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="C33" s="9" t="s">
+      <c r="C33" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="D33" s="11"/>
-      <c r="E33" s="9"/>
-      <c r="F33" s="11"/>
-      <c r="G33" s="11" t="s">
+      <c r="D33" s="5"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="5"/>
+      <c r="G33" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="H33" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="I33" s="13">
+      <c r="H33" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="I33" s="7">
         <v>30</v>
       </c>
-      <c r="J33" s="13">
+      <c r="J33" s="7">
         <v>22</v>
       </c>
-      <c r="K33" s="13">
+      <c r="K33" s="7">
         <v>52</v>
       </c>
-      <c r="L33" s="11" t="s">
+      <c r="L33" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="M33" s="9"/>
-      <c r="N33" s="14"/>
-      <c r="O33" s="15"/>
-      <c r="P33" s="15"/>
-      <c r="Q33" s="15"/>
-      <c r="R33" s="15"/>
-      <c r="S33" s="15"/>
-      <c r="T33" s="15"/>
-    </row>
-    <row r="34" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="10">
+      <c r="M33" s="6"/>
+      <c r="N33" s="6"/>
+    </row>
+    <row r="34" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="2">
         <v>601</v>
       </c>
-      <c r="B34" s="9" t="s">
+      <c r="B34" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C34" s="9" t="s">
+      <c r="C34" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="D34" s="11"/>
-      <c r="E34" s="9"/>
-      <c r="F34" s="11"/>
-      <c r="G34" s="11" t="s">
+      <c r="D34" s="2"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="H34" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="I34" s="13">
+      <c r="H34" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="I34" s="4">
         <v>44</v>
       </c>
-      <c r="J34" s="13">
+      <c r="J34" s="4">
         <v>11</v>
       </c>
-      <c r="K34" s="13">
+      <c r="K34" s="4">
         <v>55</v>
       </c>
-      <c r="L34" s="11" t="s">
+      <c r="L34" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="M34" s="9"/>
-      <c r="N34" s="14"/>
-      <c r="O34" s="15"/>
-      <c r="P34" s="15"/>
-      <c r="Q34" s="15"/>
-      <c r="R34" s="15"/>
-      <c r="S34" s="15"/>
-      <c r="T34" s="15"/>
-    </row>
-    <row r="35" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="10">
+      <c r="M34" s="3"/>
+      <c r="N34" s="3"/>
+    </row>
+    <row r="35" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="5">
         <v>602</v>
       </c>
-      <c r="B35" s="9" t="s">
+      <c r="B35" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="C35" s="9" t="s">
+      <c r="C35" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="D35" s="11"/>
-      <c r="E35" s="9" t="s">
+      <c r="D35" s="5"/>
+      <c r="E35" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="F35" s="11"/>
-      <c r="G35" s="11" t="s">
+      <c r="F35" s="5"/>
+      <c r="G35" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="H35" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="I35" s="13">
+      <c r="H35" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="I35" s="7">
         <v>44</v>
       </c>
-      <c r="J35" s="13">
+      <c r="J35" s="7">
         <v>11</v>
       </c>
-      <c r="K35" s="13">
+      <c r="K35" s="7">
         <v>55</v>
       </c>
-      <c r="L35" s="11" t="s">
+      <c r="L35" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="M35" s="9"/>
-      <c r="N35" s="14"/>
-      <c r="O35" s="15"/>
-      <c r="P35" s="15"/>
-      <c r="Q35" s="15"/>
-      <c r="R35" s="15"/>
-      <c r="S35" s="15"/>
-      <c r="T35" s="15"/>
-    </row>
-    <row r="36" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="10">
+      <c r="M35" s="6"/>
+      <c r="N35" s="6"/>
+    </row>
+    <row r="36" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="2">
         <v>603</v>
       </c>
-      <c r="B36" s="9" t="s">
+      <c r="B36" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="C36" s="9" t="s">
+      <c r="C36" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="D36" s="11"/>
-      <c r="E36" s="9" t="s">
+      <c r="D36" s="2"/>
+      <c r="E36" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="F36" s="11"/>
-      <c r="G36" s="11" t="s">
+      <c r="F36" s="2"/>
+      <c r="G36" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="H36" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="I36" s="13">
+      <c r="H36" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="I36" s="4">
         <v>7</v>
       </c>
-      <c r="J36" s="13">
+      <c r="J36" s="4">
         <v>22</v>
       </c>
-      <c r="K36" s="13">
+      <c r="K36" s="4">
         <v>29</v>
       </c>
-      <c r="L36" s="11" t="s">
+      <c r="L36" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="M36" s="9"/>
-      <c r="N36" s="14"/>
-      <c r="O36" s="15"/>
-      <c r="P36" s="15"/>
-      <c r="Q36" s="15"/>
-      <c r="R36" s="15"/>
-      <c r="S36" s="15"/>
-      <c r="T36" s="15"/>
-    </row>
-    <row r="37" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="10">
+      <c r="M36" s="3"/>
+      <c r="N36" s="3"/>
+    </row>
+    <row r="37" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="5">
         <v>604</v>
       </c>
-      <c r="B37" s="9" t="s">
+      <c r="B37" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="C37" s="9"/>
-      <c r="D37" s="11"/>
-      <c r="E37" s="9" t="s">
+      <c r="C37" s="6"/>
+      <c r="D37" s="5"/>
+      <c r="E37" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="F37" s="11"/>
-      <c r="G37" s="11"/>
-      <c r="H37" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="I37" s="13">
+      <c r="F37" s="5"/>
+      <c r="G37" s="5"/>
+      <c r="H37" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="I37" s="7">
         <v>48</v>
       </c>
-      <c r="J37" s="13">
+      <c r="J37" s="7">
         <v>22</v>
       </c>
-      <c r="K37" s="13">
+      <c r="K37" s="7">
         <v>70</v>
       </c>
-      <c r="L37" s="11" t="s">
+      <c r="L37" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="M37" s="9"/>
-      <c r="N37" s="14"/>
-      <c r="O37" s="15"/>
-      <c r="P37" s="15"/>
-      <c r="Q37" s="15"/>
-      <c r="R37" s="15"/>
-      <c r="S37" s="15"/>
-      <c r="T37" s="15"/>
-    </row>
-    <row r="38" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="10">
+      <c r="M37" s="6"/>
+      <c r="N37" s="6"/>
+    </row>
+    <row r="38" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="2">
         <v>605</v>
       </c>
-      <c r="B38" s="9" t="s">
+      <c r="B38" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="C38" s="9"/>
-      <c r="D38" s="11"/>
-      <c r="E38" s="9"/>
-      <c r="F38" s="11"/>
-      <c r="G38" s="11" t="s">
+      <c r="C38" s="3"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="3"/>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="H38" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="I38" s="13">
+      <c r="H38" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="I38" s="4">
         <v>53</v>
       </c>
-      <c r="J38" s="13">
+      <c r="J38" s="4">
         <v>11</v>
       </c>
-      <c r="K38" s="13">
+      <c r="K38" s="4">
         <v>64</v>
       </c>
-      <c r="L38" s="11" t="s">
+      <c r="L38" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="M38" s="9"/>
-      <c r="N38" s="14"/>
-      <c r="O38" s="15"/>
-      <c r="P38" s="15"/>
-      <c r="Q38" s="15"/>
-      <c r="R38" s="15"/>
-      <c r="S38" s="15"/>
-      <c r="T38" s="15"/>
-    </row>
-    <row r="39" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="10">
+      <c r="M38" s="3"/>
+      <c r="N38" s="3"/>
+    </row>
+    <row r="39" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="5">
         <v>606</v>
       </c>
-      <c r="B39" s="9" t="s">
+      <c r="B39" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="C39" s="9" t="s">
+      <c r="C39" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="D39" s="11"/>
-      <c r="E39" s="9"/>
-      <c r="F39" s="11"/>
-      <c r="G39" s="11" t="s">
+      <c r="D39" s="5"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="5"/>
+      <c r="G39" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="H39" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="I39" s="13">
+      <c r="H39" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="I39" s="7">
         <v>41</v>
       </c>
-      <c r="J39" s="13">
+      <c r="J39" s="7">
         <v>11</v>
       </c>
-      <c r="K39" s="13">
+      <c r="K39" s="7">
         <v>52</v>
       </c>
-      <c r="L39" s="11" t="s">
+      <c r="L39" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="M39" s="9"/>
-      <c r="N39" s="14"/>
-      <c r="O39" s="15"/>
-      <c r="P39" s="15"/>
-      <c r="Q39" s="15"/>
-      <c r="R39" s="15"/>
-      <c r="S39" s="15"/>
-      <c r="T39" s="15"/>
-    </row>
-    <row r="40" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="10">
+      <c r="M39" s="6"/>
+      <c r="N39" s="6"/>
+    </row>
+    <row r="40" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="2">
         <v>607</v>
       </c>
-      <c r="B40" s="9" t="s">
+      <c r="B40" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="C40" s="9" t="s">
+      <c r="C40" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="D40" s="11"/>
-      <c r="E40" s="9"/>
-      <c r="F40" s="11"/>
-      <c r="G40" s="11" t="s">
+      <c r="D40" s="2"/>
+      <c r="E40" s="3"/>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="H40" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="I40" s="13">
+      <c r="H40" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="I40" s="4">
         <v>56</v>
       </c>
-      <c r="J40" s="13">
+      <c r="J40" s="4">
         <v>8</v>
       </c>
-      <c r="K40" s="13">
+      <c r="K40" s="4">
         <v>64</v>
       </c>
-      <c r="L40" s="11" t="s">
+      <c r="L40" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="M40" s="9"/>
-      <c r="N40" s="14"/>
-      <c r="O40" s="15"/>
-      <c r="P40" s="15"/>
-      <c r="Q40" s="15"/>
-      <c r="R40" s="15"/>
-      <c r="S40" s="15"/>
-      <c r="T40" s="15"/>
-    </row>
-    <row r="41" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="10">
+      <c r="M40" s="3"/>
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="5">
         <v>608</v>
       </c>
-      <c r="B41" s="9" t="s">
+      <c r="B41" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="C41" s="9" t="s">
+      <c r="C41" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="D41" s="11" t="s">
+      <c r="D41" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="E41" s="9" t="s">
+      <c r="E41" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="F41" s="11"/>
-      <c r="G41" s="11" t="s">
+      <c r="F41" s="5"/>
+      <c r="G41" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="H41" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="I41" s="13">
+      <c r="H41" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="I41" s="7">
         <v>85</v>
       </c>
-      <c r="J41" s="13">
+      <c r="J41" s="7">
         <v>22</v>
       </c>
-      <c r="K41" s="13">
+      <c r="K41" s="7">
         <v>107</v>
       </c>
-      <c r="L41" s="11" t="s">
+      <c r="L41" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="M41" s="9"/>
-      <c r="N41" s="14"/>
-      <c r="O41" s="15"/>
-      <c r="P41" s="15"/>
-      <c r="Q41" s="15"/>
-      <c r="R41" s="15"/>
-      <c r="S41" s="15"/>
-      <c r="T41" s="15"/>
-    </row>
-    <row r="42" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="10">
+      <c r="M41" s="6"/>
+      <c r="N41" s="6"/>
+    </row>
+    <row r="42" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="2">
         <v>609</v>
       </c>
-      <c r="B42" s="9" t="s">
+      <c r="B42" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="C42" s="9" t="s">
+      <c r="C42" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="D42" s="11" t="s">
+      <c r="D42" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="E42" s="9" t="s">
+      <c r="E42" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="F42" s="11"/>
-      <c r="G42" s="11" t="s">
+      <c r="F42" s="2"/>
+      <c r="G42" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="H42" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="I42" s="13">
+      <c r="H42" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="I42" s="4">
         <v>30</v>
       </c>
-      <c r="J42" s="13">
+      <c r="J42" s="4">
         <v>20</v>
       </c>
-      <c r="K42" s="13">
+      <c r="K42" s="4">
         <v>50</v>
       </c>
-      <c r="L42" s="11" t="s">
+      <c r="L42" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="M42" s="9"/>
-      <c r="N42" s="14"/>
-      <c r="O42" s="15"/>
-      <c r="P42" s="15"/>
-      <c r="Q42" s="15"/>
-      <c r="R42" s="15"/>
-      <c r="S42" s="15"/>
-      <c r="T42" s="15"/>
-    </row>
-    <row r="43" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="10">
+      <c r="M42" s="3"/>
+      <c r="N42" s="3"/>
+    </row>
+    <row r="43" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="5">
         <v>610</v>
       </c>
-      <c r="B43" s="12" t="s">
+      <c r="B43" s="13" t="s">
         <v>153</v>
       </c>
-      <c r="C43" s="12" t="s">
+      <c r="C43" s="13" t="s">
         <v>155</v>
       </c>
-      <c r="D43" s="11">
+      <c r="D43" s="5">
         <v>1826</v>
       </c>
-      <c r="E43" s="9" t="s">
+      <c r="E43" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="F43" s="16" t="s">
+      <c r="F43" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="G43" s="11" t="s">
+      <c r="G43" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="H43" s="12" t="s">
+      <c r="H43" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="I43" s="13">
+      <c r="I43" s="7">
         <v>56</v>
       </c>
-      <c r="J43" s="13">
+      <c r="J43" s="7">
         <v>22</v>
       </c>
-      <c r="K43" s="13">
+      <c r="K43" s="7">
         <v>78</v>
       </c>
-      <c r="L43" s="11" t="s">
+      <c r="L43" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="M43" s="9" t="s">
+      <c r="M43" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="N43" s="14"/>
-      <c r="O43" s="15"/>
-      <c r="P43" s="15"/>
-      <c r="Q43" s="15"/>
-      <c r="R43" s="15"/>
-      <c r="S43" s="15"/>
-      <c r="T43" s="15"/>
-    </row>
-    <row r="44" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="10">
+      <c r="N43" s="6"/>
+    </row>
+    <row r="44" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="2">
         <v>611</v>
       </c>
-      <c r="B44" s="9" t="s">
+      <c r="B44" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="C44" s="9" t="s">
+      <c r="C44" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="D44" s="11">
+      <c r="D44" s="2">
         <v>1747</v>
       </c>
-      <c r="E44" s="9" t="s">
+      <c r="E44" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="F44" s="16" t="s">
+      <c r="F44" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G44" s="11" t="s">
+      <c r="G44" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="H44" s="12" t="s">
+      <c r="H44" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="I44" s="13">
+      <c r="I44" s="4">
         <v>113</v>
       </c>
-      <c r="J44" s="13">
+      <c r="J44" s="4">
         <v>19</v>
       </c>
-      <c r="K44" s="13">
+      <c r="K44" s="4">
         <v>132</v>
       </c>
-      <c r="L44" s="11" t="s">
+      <c r="L44" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="M44" s="9" t="s">
+      <c r="M44" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="N44" s="14"/>
-      <c r="O44" s="15"/>
-      <c r="P44" s="15"/>
-      <c r="Q44" s="15"/>
-      <c r="R44" s="15"/>
-      <c r="S44" s="15"/>
-      <c r="T44" s="15"/>
-    </row>
-    <row r="45" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="10">
+      <c r="N44" s="3"/>
+    </row>
+    <row r="45" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="5">
         <v>612</v>
       </c>
-      <c r="B45" s="9" t="s">
+      <c r="B45" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="C45" s="9" t="s">
+      <c r="C45" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="D45" s="11">
+      <c r="D45" s="5">
         <v>1780</v>
       </c>
-      <c r="E45" s="18" t="s">
+      <c r="E45" s="15" t="s">
         <v>146</v>
       </c>
-      <c r="F45" s="11" t="s">
+      <c r="F45" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G45" s="11" t="s">
+      <c r="G45" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="H45" s="9" t="s">
+      <c r="H45" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="I45" s="13">
+      <c r="I45" s="7">
         <v>36</v>
       </c>
-      <c r="J45" s="13">
+      <c r="J45" s="7">
         <v>19</v>
       </c>
-      <c r="K45" s="13">
+      <c r="K45" s="7">
         <v>55</v>
       </c>
-      <c r="L45" s="11" t="s">
+      <c r="L45" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="M45" s="9" t="s">
+      <c r="M45" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="N45" s="14"/>
-      <c r="O45" s="15"/>
-      <c r="P45" s="15"/>
-      <c r="Q45" s="15"/>
-      <c r="R45" s="15"/>
-      <c r="S45" s="15"/>
-      <c r="T45" s="15"/>
-    </row>
-    <row r="46" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="10">
+      <c r="N45" s="6"/>
+    </row>
+    <row r="46" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="2">
         <v>613</v>
       </c>
-      <c r="B46" s="9" t="s">
+      <c r="B46" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="C46" s="9" t="s">
+      <c r="C46" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="D46" s="11">
+      <c r="D46" s="2">
         <v>1762</v>
       </c>
-      <c r="E46" s="9" t="s">
+      <c r="E46" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="F46" s="11" t="s">
+      <c r="F46" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="G46" s="11" t="s">
+      <c r="G46" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="H46" s="12" t="s">
+      <c r="H46" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="I46" s="13">
+      <c r="I46" s="4">
         <v>61</v>
       </c>
-      <c r="J46" s="13">
+      <c r="J46" s="4">
         <v>22</v>
       </c>
-      <c r="K46" s="13">
+      <c r="K46" s="4">
         <v>83</v>
       </c>
-      <c r="L46" s="11" t="s">
+      <c r="L46" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="M46" s="9"/>
-      <c r="N46" s="14"/>
-      <c r="O46" s="15"/>
-      <c r="P46" s="15"/>
-      <c r="Q46" s="15"/>
-      <c r="R46" s="15"/>
-      <c r="S46" s="15"/>
-      <c r="T46" s="15"/>
-    </row>
-    <row r="47" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="19">
+      <c r="M46" s="3"/>
+      <c r="N46" s="3"/>
+    </row>
+    <row r="47" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="2">
         <v>614</v>
       </c>
-      <c r="B47" s="20" t="s">
+      <c r="B47" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="C47" s="20" t="s">
+      <c r="C47" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="D47" s="21">
+      <c r="D47" s="5">
         <v>1904</v>
       </c>
-      <c r="E47" s="20" t="s">
+      <c r="E47" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="F47" s="21" t="s">
+      <c r="F47" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G47" s="21" t="s">
+      <c r="G47" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="H47" s="20" t="s">
+      <c r="H47" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="I47" s="22">
+      <c r="I47" s="7">
         <v>11</v>
       </c>
-      <c r="J47" s="22">
+      <c r="J47" s="7">
         <v>5</v>
       </c>
-      <c r="K47" s="22">
+      <c r="K47" s="7">
         <v>16</v>
       </c>
-      <c r="L47" s="21" t="s">
+      <c r="L47" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="M47" s="20" t="s">
+      <c r="M47" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="N47" s="23"/>
-      <c r="O47" s="15"/>
-      <c r="P47" s="15"/>
-      <c r="Q47" s="15"/>
-      <c r="R47" s="15"/>
-      <c r="S47" s="15"/>
-      <c r="T47" s="15"/>
-    </row>
-    <row r="48" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="3" t="s">
+      <c r="N47" s="3"/>
+    </row>
+    <row r="48" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="B48" s="4"/>
-      <c r="C48" s="4"/>
-      <c r="D48" s="4"/>
-      <c r="E48" s="4"/>
-      <c r="F48" s="4"/>
-      <c r="G48" s="4"/>
-      <c r="H48" s="4"/>
-      <c r="I48" s="5">
+      <c r="B48" s="9"/>
+      <c r="C48" s="9"/>
+      <c r="D48" s="9"/>
+      <c r="E48" s="9"/>
+      <c r="F48" s="9"/>
+      <c r="G48" s="9"/>
+      <c r="H48" s="9"/>
+      <c r="I48" s="10">
         <f>SUM(I1:I47)</f>
         <v>2518</v>
       </c>
-      <c r="J48" s="5">
+      <c r="J48" s="10">
         <f>SUM(J1:J47)</f>
         <v>598.5</v>
       </c>
-      <c r="K48" s="5">
+      <c r="K48" s="10">
         <f>SUM(K1:K47)</f>
         <v>3116.5</v>
       </c>
-      <c r="L48" s="4"/>
-      <c r="M48" s="4"/>
-      <c r="N48" s="4"/>
+      <c r="L48" s="9"/>
+      <c r="M48" s="9"/>
+      <c r="N48" s="9"/>
     </row>
     <row r="49" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="1"/>
-      <c r="L49" s="1"/>
-      <c r="M49" s="2"/>
-      <c r="N49" s="2"/>
+      <c r="A49" s="5"/>
+      <c r="L49" s="5"/>
+      <c r="M49" s="6"/>
+      <c r="N49" s="6"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:N1" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N49">
+      <sortCondition ref="A1"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <tableParts count="1">
-    <tablePart r:id="rId2"/>
-  </tableParts>
 </worksheet>
 </file>
--- a/MAPAS.xlsx
+++ b/MAPAS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GITHUB\coleccion-mapas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9AA9F9D-3E54-452F-AABA-C774817A0D76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC265267-3CB6-4929-91C4-1545F01152E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="193">
   <si>
     <t>SKU</t>
   </si>
@@ -47,12 +47,6 @@
     <t>Autor/es</t>
   </si>
   <si>
-    <t>Fecha del mapa</t>
-  </si>
-  <si>
-    <t>Dimensiones (cm)</t>
-  </si>
-  <si>
     <t>Coloreado</t>
   </si>
   <si>
@@ -122,9 +116,6 @@
     <t>Catawiki - Elybetty</t>
   </si>
   <si>
-    <t>América meridional</t>
-  </si>
-  <si>
     <t>Jacques Chiquet</t>
   </si>
   <si>
@@ -170,15 +161,6 @@
     <t>28/02/2025</t>
   </si>
   <si>
-    <t>Mapa Mundi Hérisson</t>
-  </si>
-  <si>
-    <t>1801-1820</t>
-  </si>
-  <si>
-    <t>Australia polo sur</t>
-  </si>
-  <si>
     <t>Desconocido 1701</t>
   </si>
   <si>
@@ -236,21 +218,9 @@
     <t>08/05/2025</t>
   </si>
   <si>
-    <t>mapamundi</t>
-  </si>
-  <si>
-    <t>MOUTARD</t>
-  </si>
-  <si>
-    <t>ARGENTINA</t>
-  </si>
-  <si>
     <t>14/05/2025</t>
   </si>
   <si>
-    <t>MOUTARD-DE LA PORTE</t>
-  </si>
-  <si>
     <t>Amerique Meridionale</t>
   </si>
   <si>
@@ -305,12 +275,6 @@
     <t>Sudamérica</t>
   </si>
   <si>
-    <t>La Haye</t>
-  </si>
-  <si>
-    <t>Sudamérica Meridional</t>
-  </si>
-  <si>
     <t>La Haye, P. de Hondt / J.N. Bellin / A.F. Prevost</t>
   </si>
   <si>
@@ -588,6 +552,69 @@
   </si>
   <si>
     <t>Atlas Encyclopédique contenant la géographie ancienne et quelques cartes sur la géographie du Moyen-Age, la géographie moderne et les cartes relatives à la géographie physique par M. BONNE et M. DESMARET. Hôtel de Thou, 1787</t>
+  </si>
+  <si>
+    <t>Fecha</t>
+  </si>
+  <si>
+    <t>Dimensiones</t>
+  </si>
+  <si>
+    <t>Si</t>
+  </si>
+  <si>
+    <t>26 x 20</t>
+  </si>
+  <si>
+    <t>L'Amerique Meridionale</t>
+  </si>
+  <si>
+    <t>Le nouveau et curieux ATLAS geographique et historique ou Le divertissement des Empereurs, Roys, et Princes tant dans le guerre que dans le paix...</t>
+  </si>
+  <si>
+    <t>27 x 20</t>
+  </si>
+  <si>
+    <t>Mappe-Monde divisée en ses quatre parties</t>
+  </si>
+  <si>
+    <t>Hérisson</t>
+  </si>
+  <si>
+    <t>"Petit Atlas contenant la Géographie Universelle Ancienne et Moderne". Par Hérisson, Ingénieur-Géographe. Paris, 1811</t>
+  </si>
+  <si>
+    <t>26 x 21,5</t>
+  </si>
+  <si>
+    <t>Polo Sur - Australia, Nueva Zelanda, África, América</t>
+  </si>
+  <si>
+    <t>Mapa poco habitual. Autor desconocido</t>
+  </si>
+  <si>
+    <t>Mappe-Monde ou Descriptio du Globe Terrestre -</t>
+  </si>
+  <si>
+    <t>Moutard - Delaporte</t>
+  </si>
+  <si>
+    <t>Atlas ou collection de cartes géographiques pour l'intelligence du voyageur françois ou la connoissance de l'ancien et du nouveau monde</t>
+  </si>
+  <si>
+    <t>L'AMÉRIQUE Méridinale divisée en ses principaux ETATS</t>
+  </si>
+  <si>
+    <t>"Atlas ou Collection de Cartes Geographiques......... a PARIS, 1787."</t>
+  </si>
+  <si>
+    <t>AMÉRIQUE MÉRIDIONALE</t>
+  </si>
+  <si>
+    <t>Carte reduite de la partie, la plus Meridionale de l'Amerique</t>
+  </si>
+  <si>
+    <t>27 x 21</t>
   </si>
 </sst>
 </file>
@@ -780,7 +807,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -855,23 +882,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="18">
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1168,6 +1183,15 @@
           <bgColor auto="1"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1344,21 +1368,24 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0137933E-08B7-4D8E-A3A8-E50FCA760235}" name="Tabla1" displayName="Tabla1" ref="A1:N47" totalsRowShown="0" headerRowDxfId="17" dataDxfId="15" headerRowBorderDxfId="16" tableBorderDxfId="14">
   <autoFilter ref="A1:N47" xr:uid="{0137933E-08B7-4D8E-A3A8-E50FCA760235}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:N32">
+    <sortCondition ref="L1:L47"/>
+  </sortState>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{0B4683B1-BDF2-4C1C-9132-ABAEAB75C15B}" name="SKU" dataDxfId="13"/>
     <tableColumn id="2" xr3:uid="{EF4B33BB-CFA3-4BDD-99C9-F59CB1A4728B}" name="Título" dataDxfId="12"/>
     <tableColumn id="3" xr3:uid="{524E1B45-DCB4-44DC-A051-3C9317903257}" name="Autor/es" dataDxfId="11"/>
-    <tableColumn id="4" xr3:uid="{EE649AF3-D6C7-4A3E-A015-128D9C7286EA}" name="Fecha del mapa" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{6DF358FA-715A-41A7-9906-7BF69B7718A3}" name="Dimensiones (cm)" dataDxfId="0"/>
-    <tableColumn id="6" xr3:uid="{3DE6D0A0-B7A0-42DD-980B-480E7FF7E5A8}" name="Coloreado" dataDxfId="9"/>
-    <tableColumn id="7" xr3:uid="{61B5095D-DE7A-4B30-AEAA-9A2DB60681D5}" name="Fecha de compra" dataDxfId="8"/>
-    <tableColumn id="8" xr3:uid="{13CAC9B6-50EC-4F6E-A1ED-53998F03984E}" name="Vendedor" dataDxfId="7"/>
-    <tableColumn id="9" xr3:uid="{306CDCE0-B89D-4A9B-8346-2EE0D1B92965}" name="Precio" dataDxfId="6"/>
-    <tableColumn id="10" xr3:uid="{7F1BD210-292C-4209-A4C3-6A477BD9086E}" name="Portes" dataDxfId="5"/>
-    <tableColumn id="11" xr3:uid="{1E0CF666-8B35-4863-837A-B4CF8D3AB40E}" name="Total" dataDxfId="4"/>
-    <tableColumn id="12" xr3:uid="{CEF4B379-641A-48F6-8FBF-D8213CFE7E55}" name="Archivador" dataDxfId="3"/>
-    <tableColumn id="13" xr3:uid="{ED113F52-3FB9-4C04-B11B-20AC23DF2799}" name="Notas" dataDxfId="2"/>
-    <tableColumn id="14" xr3:uid="{A3064BD6-D79A-46DA-90EF-8E09E6FDDDC8}" name="Anotaciones" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{EE649AF3-D6C7-4A3E-A015-128D9C7286EA}" name="Fecha" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{6DF358FA-715A-41A7-9906-7BF69B7718A3}" name="Dimensiones" dataDxfId="9"/>
+    <tableColumn id="6" xr3:uid="{3DE6D0A0-B7A0-42DD-980B-480E7FF7E5A8}" name="Coloreado" dataDxfId="8"/>
+    <tableColumn id="7" xr3:uid="{61B5095D-DE7A-4B30-AEAA-9A2DB60681D5}" name="Fecha de compra" dataDxfId="7"/>
+    <tableColumn id="8" xr3:uid="{13CAC9B6-50EC-4F6E-A1ED-53998F03984E}" name="Vendedor" dataDxfId="6"/>
+    <tableColumn id="9" xr3:uid="{306CDCE0-B89D-4A9B-8346-2EE0D1B92965}" name="Precio" dataDxfId="5"/>
+    <tableColumn id="10" xr3:uid="{7F1BD210-292C-4209-A4C3-6A477BD9086E}" name="Portes" dataDxfId="4"/>
+    <tableColumn id="11" xr3:uid="{1E0CF666-8B35-4863-837A-B4CF8D3AB40E}" name="Total" dataDxfId="3"/>
+    <tableColumn id="12" xr3:uid="{CEF4B379-641A-48F6-8FBF-D8213CFE7E55}" name="Archivador" dataDxfId="2"/>
+    <tableColumn id="13" xr3:uid="{ED113F52-3FB9-4C04-B11B-20AC23DF2799}" name="Notas" dataDxfId="1"/>
+    <tableColumn id="14" xr3:uid="{A3064BD6-D79A-46DA-90EF-8E09E6FDDDC8}" name="Anotaciones" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1675,37 +1702,37 @@
         <v>2</v>
       </c>
       <c r="D1" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="F1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="G1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="H1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="I1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="J1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="K1" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="L1" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="M1" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="N1" s="8" t="s">
         <v>11</v>
-      </c>
-      <c r="M1" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="8" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -1713,25 +1740,25 @@
         <v>139</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D2" s="11">
         <v>1798</v>
       </c>
       <c r="E2" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="G2" s="11" t="s">
-        <v>18</v>
-      </c>
       <c r="H2" s="12" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="I2" s="13">
         <v>28</v>
@@ -1743,10 +1770,10 @@
         <v>36</v>
       </c>
       <c r="L2" s="11" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="M2" s="10" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="N2" s="14"/>
     </row>
@@ -1755,25 +1782,25 @@
         <v>140</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D3" s="11">
         <v>1798</v>
       </c>
       <c r="E3" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" s="11" t="s">
-        <v>18</v>
-      </c>
       <c r="H3" s="12" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="I3" s="13">
         <v>28</v>
@@ -1785,10 +1812,10 @@
         <v>36</v>
       </c>
       <c r="L3" s="11" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="M3" s="10" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="N3" s="14"/>
     </row>
@@ -1797,25 +1824,25 @@
         <v>175</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C4" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="D4" s="11">
+        <v>1655</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="F4" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4" s="12" t="s">
         <v>106</v>
-      </c>
-      <c r="D4" s="26">
-        <v>1655</v>
-      </c>
-      <c r="E4" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="F4" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="G4" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="H4" s="12" t="s">
-        <v>118</v>
       </c>
       <c r="I4" s="13">
         <v>69</v>
@@ -1828,10 +1855,10 @@
       </c>
       <c r="L4" s="11"/>
       <c r="M4" s="12" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="N4" s="16" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -1839,25 +1866,25 @@
         <v>219</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="D5" s="11">
         <v>1780</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G5" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="H5" s="10" t="s">
         <v>25</v>
-      </c>
-      <c r="H5" s="10" t="s">
-        <v>27</v>
       </c>
       <c r="I5" s="13">
         <v>30</v>
@@ -1869,10 +1896,10 @@
         <v>45</v>
       </c>
       <c r="L5" s="11" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="M5" s="12" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="N5" s="14"/>
     </row>
@@ -1881,25 +1908,25 @@
         <v>230</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="D6" s="11">
         <v>1635</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="I6" s="13">
         <v>45</v>
@@ -1912,7 +1939,7 @@
       </c>
       <c r="L6" s="11"/>
       <c r="M6" s="12" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="N6" s="14"/>
     </row>
@@ -1921,21 +1948,25 @@
         <v>574</v>
       </c>
       <c r="B7" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="11">
+        <v>1719</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="G7" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="E7" s="11"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="11" t="s">
-        <v>31</v>
-      </c>
       <c r="H7" s="10" t="s">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="I7" s="13">
         <v>74</v>
@@ -1947,9 +1978,11 @@
         <v>96</v>
       </c>
       <c r="L7" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="M7" s="10"/>
+        <v>119</v>
+      </c>
+      <c r="M7" s="10" t="s">
+        <v>177</v>
+      </c>
       <c r="N7" s="14"/>
     </row>
     <row r="8" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -1957,25 +1990,25 @@
         <v>575</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H8" s="12" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="I8" s="13">
         <v>34</v>
@@ -1988,7 +2021,7 @@
       </c>
       <c r="L8" s="11"/>
       <c r="M8" s="10" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="N8" s="14"/>
     </row>
@@ -1997,25 +2030,25 @@
         <v>576</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H9" s="12" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="I9" s="13">
         <v>34</v>
@@ -2028,7 +2061,7 @@
       </c>
       <c r="L9" s="11"/>
       <c r="M9" s="10" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="N9" s="14"/>
     </row>
@@ -2037,21 +2070,21 @@
         <v>577</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
       <c r="G10" s="11" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="I10" s="13">
         <v>56</v>
@@ -2063,7 +2096,7 @@
         <v>64</v>
       </c>
       <c r="L10" s="11" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="M10" s="10"/>
       <c r="N10" s="14"/>
@@ -2073,21 +2106,21 @@
         <v>578</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
       <c r="G11" s="11" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="I11" s="13">
         <v>56</v>
@@ -2099,7 +2132,7 @@
         <v>64</v>
       </c>
       <c r="L11" s="11" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="M11" s="10"/>
       <c r="N11" s="14"/>
@@ -2109,19 +2142,19 @@
         <v>579</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D12" s="11"/>
       <c r="E12" s="11"/>
       <c r="F12" s="11"/>
       <c r="G12" s="11" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="I12" s="13">
         <v>142</v>
@@ -2133,7 +2166,7 @@
         <v>153</v>
       </c>
       <c r="L12" s="11" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="M12" s="10"/>
       <c r="N12" s="14"/>
@@ -2143,25 +2176,25 @@
         <v>580</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="D13" s="11">
         <v>1754</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="I13" s="13">
         <v>40</v>
@@ -2173,7 +2206,7 @@
         <v>51</v>
       </c>
       <c r="L13" s="11" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="M13" s="10"/>
       <c r="N13" s="14"/>
@@ -2183,19 +2216,25 @@
         <v>581</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="C14" s="10"/>
-      <c r="D14" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
+        <v>179</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="D14" s="11">
+        <v>1811</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>174</v>
+      </c>
       <c r="G14" s="11" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>146</v>
+        <v>128</v>
       </c>
       <c r="I14" s="13">
         <v>90</v>
@@ -2207,9 +2246,11 @@
         <v>110</v>
       </c>
       <c r="L14" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="M14" s="10"/>
+        <v>119</v>
+      </c>
+      <c r="M14" s="10" t="s">
+        <v>181</v>
+      </c>
       <c r="N14" s="14"/>
     </row>
     <row r="15" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -2217,21 +2258,25 @@
         <v>582</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>46</v>
+        <v>183</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D15" s="26">
+        <v>41</v>
+      </c>
+      <c r="D15" s="11">
         <v>1720</v>
       </c>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
+      <c r="E15" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="F15" s="11" t="s">
+        <v>15</v>
+      </c>
       <c r="G15" s="11" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>146</v>
+        <v>128</v>
       </c>
       <c r="I15" s="13">
         <v>112</v>
@@ -2243,9 +2288,11 @@
         <v>132</v>
       </c>
       <c r="L15" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="M15" s="10"/>
+        <v>119</v>
+      </c>
+      <c r="M15" s="10" t="s">
+        <v>184</v>
+      </c>
       <c r="N15" s="14"/>
     </row>
     <row r="16" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -2253,25 +2300,25 @@
         <v>583</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="D16" s="11">
         <v>1754</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="H16" s="12" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="I16" s="13">
         <v>24</v>
@@ -2281,10 +2328,10 @@
         <v>24</v>
       </c>
       <c r="L16" s="11" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="M16" s="10" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="N16" s="14"/>
     </row>
@@ -2293,25 +2340,25 @@
         <v>584</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="D17" s="11">
         <v>1754</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="H17" s="12" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="I17" s="13">
         <v>24</v>
@@ -2321,10 +2368,10 @@
         <v>24</v>
       </c>
       <c r="L17" s="11" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="M17" s="10" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="N17" s="14"/>
     </row>
@@ -2333,25 +2380,25 @@
         <v>585</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="D18" s="11">
         <v>1774</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="H18" s="10" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="I18" s="13">
         <v>30</v>
@@ -2363,10 +2410,10 @@
         <v>37.5</v>
       </c>
       <c r="L18" s="11" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="M18" s="10" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="N18" s="14"/>
     </row>
@@ -2375,19 +2422,19 @@
         <v>586</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="D19" s="11"/>
       <c r="E19" s="11"/>
       <c r="F19" s="11"/>
       <c r="G19" s="11" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="I19" s="13">
         <v>91</v>
@@ -2399,7 +2446,7 @@
         <v>107</v>
       </c>
       <c r="L19" s="11" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="M19" s="10"/>
       <c r="N19" s="14"/>
@@ -2409,19 +2456,19 @@
         <v>587</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D20" s="11"/>
       <c r="E20" s="11"/>
       <c r="F20" s="11"/>
       <c r="G20" s="11" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="H20" s="10" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="I20" s="13">
         <v>91</v>
@@ -2433,7 +2480,7 @@
         <v>113</v>
       </c>
       <c r="L20" s="11" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="M20" s="10"/>
       <c r="N20" s="14"/>
@@ -2443,25 +2490,25 @@
         <v>588</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D21" s="11">
         <v>1787</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G21" s="11" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="I21" s="13">
         <v>112</v>
@@ -2473,10 +2520,10 @@
         <v>123</v>
       </c>
       <c r="L21" s="11" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="M21" s="10" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="N21" s="14"/>
     </row>
@@ -2485,25 +2532,25 @@
         <v>589</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="D22" s="11">
         <v>1780</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G22" s="11" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="I22" s="13">
         <v>51</v>
@@ -2515,10 +2562,10 @@
         <v>62</v>
       </c>
       <c r="L22" s="11" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="M22" s="10" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="N22" s="14"/>
     </row>
@@ -2527,19 +2574,19 @@
         <v>590</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="D23" s="11"/>
       <c r="E23" s="11"/>
       <c r="F23" s="11"/>
       <c r="G23" s="11" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="I23" s="13">
         <v>28</v>
@@ -2549,7 +2596,7 @@
         <v>28</v>
       </c>
       <c r="L23" s="11" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="M23" s="10"/>
       <c r="N23" s="14"/>
@@ -2559,19 +2606,19 @@
         <v>591</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D24" s="11"/>
       <c r="E24" s="11"/>
       <c r="F24" s="11"/>
       <c r="G24" s="11" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="I24" s="13">
         <v>28</v>
@@ -2581,7 +2628,7 @@
         <v>28</v>
       </c>
       <c r="L24" s="11" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="M24" s="10"/>
       <c r="N24" s="14"/>
@@ -2591,25 +2638,25 @@
         <v>592</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G25" s="22">
         <v>45722</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="I25" s="13">
         <v>112</v>
@@ -2621,10 +2668,10 @@
         <v>134</v>
       </c>
       <c r="L25" s="11" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="M25" s="10" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="N25" s="14"/>
     </row>
@@ -2633,19 +2680,19 @@
         <v>593</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D26" s="11"/>
       <c r="E26" s="11"/>
       <c r="F26" s="11"/>
       <c r="G26" s="11" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H26" s="10" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="I26" s="13">
         <v>106</v>
@@ -2657,7 +2704,7 @@
         <v>117</v>
       </c>
       <c r="L26" s="11" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="M26" s="10"/>
       <c r="N26" s="14"/>
@@ -2667,19 +2714,25 @@
         <v>594</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>66</v>
+        <v>185</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="D27" s="11"/>
-      <c r="E27" s="11"/>
-      <c r="F27" s="11"/>
+        <v>186</v>
+      </c>
+      <c r="D27" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="E27" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="F27" s="11" t="s">
+        <v>15</v>
+      </c>
       <c r="G27" s="11" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="I27" s="13">
         <v>83</v>
@@ -2691,9 +2744,11 @@
         <v>94</v>
       </c>
       <c r="L27" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="M27" s="10"/>
+        <v>119</v>
+      </c>
+      <c r="M27" s="10" t="s">
+        <v>187</v>
+      </c>
       <c r="N27" s="14"/>
     </row>
     <row r="28" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -2701,25 +2756,25 @@
         <v>595</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G28" s="11" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="H28" s="10" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="I28" s="13">
         <v>13</v>
@@ -2731,10 +2786,10 @@
         <v>19</v>
       </c>
       <c r="L28" s="11" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="M28" s="10" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="N28" s="14"/>
     </row>
@@ -2743,25 +2798,25 @@
         <v>596</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="F29" s="11" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G29" s="11" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="I29" s="13">
         <v>13</v>
@@ -2773,10 +2828,10 @@
         <v>19</v>
       </c>
       <c r="L29" s="11" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="M29" s="10" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="N29" s="14"/>
     </row>
@@ -2785,19 +2840,25 @@
         <v>597</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>68</v>
+        <v>188</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="D30" s="11"/>
-      <c r="E30" s="11"/>
-      <c r="F30" s="11"/>
+        <v>186</v>
+      </c>
+      <c r="D30" s="11">
+        <v>1786</v>
+      </c>
+      <c r="E30" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="F30" s="11" t="s">
+        <v>15</v>
+      </c>
       <c r="G30" s="11" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="H30" s="10" t="s">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="I30" s="13">
         <v>56</v>
@@ -2809,9 +2870,11 @@
         <v>67</v>
       </c>
       <c r="L30" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="M30" s="10"/>
+        <v>119</v>
+      </c>
+      <c r="M30" s="10" t="s">
+        <v>189</v>
+      </c>
       <c r="N30" s="14"/>
     </row>
     <row r="31" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -2819,25 +2882,25 @@
         <v>598</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G31" s="11" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="I31" s="13">
         <v>30</v>
@@ -2849,10 +2912,10 @@
         <v>58</v>
       </c>
       <c r="L31" s="11" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="M31" s="12" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="N31" s="14"/>
     </row>
@@ -2861,21 +2924,21 @@
         <v>599</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="E32" s="11"/>
       <c r="F32" s="11"/>
       <c r="G32" s="11" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="H32" s="10" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="I32" s="13">
         <v>73</v>
@@ -2895,25 +2958,25 @@
         <v>600</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="E33" s="15" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="F33" s="15" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G33" s="11" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="I33" s="13">
         <v>30</v>
@@ -2925,10 +2988,10 @@
         <v>52</v>
       </c>
       <c r="L33" s="11" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="M33" s="10" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="N33" s="14"/>
     </row>
@@ -2937,19 +3000,19 @@
         <v>601</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="D34" s="11"/>
       <c r="E34" s="11"/>
       <c r="F34" s="11"/>
       <c r="G34" s="11" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="H34" s="10" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="I34" s="13">
         <v>44</v>
@@ -2961,7 +3024,7 @@
         <v>55</v>
       </c>
       <c r="L34" s="11" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="M34" s="10"/>
       <c r="N34" s="14"/>
@@ -2971,21 +3034,21 @@
         <v>602</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="D35" s="11"/>
       <c r="E35" s="11" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="F35" s="11"/>
       <c r="G35" s="11" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="I35" s="13">
         <v>44</v>
@@ -2997,7 +3060,7 @@
         <v>55</v>
       </c>
       <c r="L35" s="11" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="M35" s="10"/>
       <c r="N35" s="14"/>
@@ -3007,21 +3070,21 @@
         <v>603</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="D36" s="11"/>
       <c r="E36" s="11" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="F36" s="11"/>
       <c r="G36" s="11" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="H36" s="10" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="I36" s="13">
         <v>7</v>
@@ -3033,7 +3096,7 @@
         <v>29</v>
       </c>
       <c r="L36" s="11" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="M36" s="10"/>
       <c r="N36" s="14"/>
@@ -3043,17 +3106,17 @@
         <v>604</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="11"/>
       <c r="E37" s="11" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="F37" s="11"/>
       <c r="G37" s="11"/>
       <c r="H37" s="10" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="I37" s="13">
         <v>48</v>
@@ -3065,7 +3128,7 @@
         <v>70</v>
       </c>
       <c r="L37" s="11" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="M37" s="10"/>
       <c r="N37" s="14"/>
@@ -3075,25 +3138,25 @@
         <v>605</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="D38" s="15" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="E38" s="15" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="F38" s="15" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G38" s="11" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="H38" s="10" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="I38" s="13">
         <v>53</v>
@@ -3105,10 +3168,10 @@
         <v>64</v>
       </c>
       <c r="L38" s="11" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="M38" s="10" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="N38" s="14"/>
     </row>
@@ -3117,19 +3180,25 @@
         <v>606</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>88</v>
+        <v>190</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="D39" s="11"/>
-      <c r="E39" s="11"/>
-      <c r="F39" s="11"/>
+        <v>79</v>
+      </c>
+      <c r="D39" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="E39" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="F39" s="11" t="s">
+        <v>15</v>
+      </c>
       <c r="G39" s="11" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="I39" s="13">
         <v>41</v>
@@ -3141,9 +3210,11 @@
         <v>52</v>
       </c>
       <c r="L39" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="M39" s="10"/>
+        <v>119</v>
+      </c>
+      <c r="M39" s="10" t="s">
+        <v>159</v>
+      </c>
       <c r="N39" s="14"/>
     </row>
     <row r="40" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -3151,19 +3222,25 @@
         <v>607</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>90</v>
+        <v>191</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="D40" s="11"/>
-      <c r="E40" s="11"/>
-      <c r="F40" s="11"/>
+        <v>79</v>
+      </c>
+      <c r="D40" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="E40" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="F40" s="11" t="s">
+        <v>15</v>
+      </c>
       <c r="G40" s="11" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="H40" s="10" t="s">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="I40" s="13">
         <v>56</v>
@@ -3175,9 +3252,11 @@
         <v>64</v>
       </c>
       <c r="L40" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="M40" s="10"/>
+        <v>119</v>
+      </c>
+      <c r="M40" s="10" t="s">
+        <v>159</v>
+      </c>
       <c r="N40" s="14"/>
     </row>
     <row r="41" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -3185,23 +3264,23 @@
         <v>608</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>182</v>
+        <v>170</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="D41" s="26">
+        <v>81</v>
+      </c>
+      <c r="D41" s="11">
         <v>1787</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="F41" s="11"/>
       <c r="G41" s="11" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H41" s="12" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="I41" s="13">
         <v>85</v>
@@ -3213,10 +3292,10 @@
         <v>107</v>
       </c>
       <c r="L41" s="11" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="M41" s="12" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="N41" s="14"/>
     </row>
@@ -3225,23 +3304,23 @@
         <v>609</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="F42" s="11"/>
       <c r="G42" s="11" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="H42" s="10" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="I42" s="13">
         <v>30</v>
@@ -3253,7 +3332,7 @@
         <v>50</v>
       </c>
       <c r="L42" s="11" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="M42" s="10"/>
       <c r="N42" s="14"/>
@@ -3263,25 +3342,25 @@
         <v>610</v>
       </c>
       <c r="B43" s="12" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="D43" s="11">
         <v>1826</v>
       </c>
       <c r="E43" s="11" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="F43" s="15" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G43" s="11" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="H43" s="12" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="I43" s="13">
         <v>56</v>
@@ -3293,10 +3372,10 @@
         <v>78</v>
       </c>
       <c r="L43" s="11" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="M43" s="10" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="N43" s="14"/>
     </row>
@@ -3305,25 +3384,25 @@
         <v>611</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="C44" s="10" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="D44" s="11">
         <v>1747</v>
       </c>
       <c r="E44" s="11" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="F44" s="15" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G44" s="11" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="H44" s="12" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="I44" s="13">
         <v>113</v>
@@ -3335,10 +3414,10 @@
         <v>132</v>
       </c>
       <c r="L44" s="11" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="M44" s="10" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="N44" s="14"/>
     </row>
@@ -3347,25 +3426,25 @@
         <v>612</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="C45" s="10" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="D45" s="11">
         <v>1780</v>
       </c>
       <c r="E45" s="23" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G45" s="11" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="I45" s="13">
         <v>36</v>
@@ -3377,10 +3456,10 @@
         <v>55</v>
       </c>
       <c r="L45" s="11" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="M45" s="10" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="N45" s="14"/>
     </row>
@@ -3389,25 +3468,25 @@
         <v>613</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="C46" s="10" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="D46" s="11">
         <v>1762</v>
       </c>
       <c r="E46" s="11" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G46" s="11" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="H46" s="12" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="I46" s="13">
         <v>61</v>
@@ -3419,10 +3498,10 @@
         <v>83</v>
       </c>
       <c r="L46" s="11" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="M46" s="10" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="N46" s="14"/>
     </row>
@@ -3431,25 +3510,25 @@
         <v>614</v>
       </c>
       <c r="B47" s="18" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="C47" s="18" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="D47" s="19">
         <v>1904</v>
       </c>
       <c r="E47" s="19" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
       <c r="F47" s="19" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G47" s="19" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="H47" s="18" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="I47" s="20">
         <v>11</v>
@@ -3461,16 +3540,16 @@
         <v>16</v>
       </c>
       <c r="L47" s="19" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="M47" s="18" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="N47" s="21"/>
     </row>
     <row r="48" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
